--- a/ВКР/Ссылки.xlsx
+++ b/ВКР/Ссылки.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ИВАН\Desktop\лабы\2 курс\Labs\ВКР\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31DAEC1-5BE4-49DE-B00F-31E37831F4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC03D213-4D88-425A-BE38-E6B1A8E5C347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Рисунки" sheetId="1" r:id="rId1"/>
@@ -667,7 +667,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
         <v>21</v>
@@ -975,7 +975,7 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40">
         <v>57</v>
